--- a/src/attributions/attributions_ig_traj_238.xlsx
+++ b/src/attributions/attributions_ig_traj_238.xlsx
@@ -999,19 +999,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3452417580060654</v>
+        <v>0.2080532843332191</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.08261506467728795</v>
+        <v>-0.1797826944559005</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2215582424309029</v>
+        <v>0.1144135535724268</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1023,103 +1023,103 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1688968867201568</v>
+        <v>0.08703419178639529</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.02933815257951094</v>
+        <v>-0.1399317533438643</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.01672700905719935</v>
+        <v>0.008441038868514326</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002618079851637398</v>
+        <v>0.1580582561380608</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.004339126665139236</v>
+        <v>-0.09230855588073193</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.07635475768118961</v>
+        <v>0.2059006819569592</v>
       </c>
       <c r="X2" t="n">
         <v>-0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.04336407163406774</v>
+        <v>-0.2218048112983806</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.03040857114302248</v>
+        <v>-0.04920662269791221</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.05905272439853523</v>
+        <v>0.1000277767826751</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.1266037562053799</v>
+        <v>0.1541503839754077</v>
       </c>
       <c r="AL2" t="n">
         <v>-0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.03839294734884099</v>
+        <v>-0.1137825678629702</v>
       </c>
       <c r="AN2" t="n">
         <v>-0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.02733219441321614</v>
+        <v>0.1616036141246567</v>
       </c>
       <c r="AP2" t="n">
         <v>-0</v>
@@ -1131,25 +1131,25 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.303279369784314</v>
+        <v>0.3205378158263797</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.2584662969013808</v>
+        <v>-0.2477522332975519</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.515092452898108</v>
+        <v>0.1508741164744801</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -1158,22 +1158,22 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.234551661729016</v>
+        <v>-0.07272963286154474</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.09344244250468065</v>
+        <v>-0.1042963736102188</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.02594922904810832</v>
+        <v>-0.0552396480004464</v>
       </c>
       <c r="BH2" t="n">
         <v>-0</v>
@@ -1185,25 +1185,25 @@
         <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.03349896152617389</v>
+        <v>-0.1350931113829535</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.02160204408278227</v>
+        <v>0.1215026127754351</v>
       </c>
       <c r="BO2" t="n">
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.1134295304680484</v>
+        <v>-0.05488789366361235</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
@@ -1212,28 +1212,28 @@
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.1150649839083074</v>
+        <v>0.2246691753433546</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.09187082730208117</v>
+        <v>-0.1217578283680718</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.1753995182764498</v>
+        <v>-0.05941513144473162</v>
       </c>
       <c r="BZ2" t="n">
         <v>-0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1242,19 +1242,19 @@
         <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.1035280389567418</v>
+        <v>-0.1163220087831819</v>
       </c>
       <c r="CE2" t="n">
         <v>0</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.01258923604465515</v>
+        <v>0.1132223834334971</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.09464753852374616</v>
+        <v>-0.07426920689856122</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
@@ -1263,28 +1263,28 @@
         <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.001889317967430027</v>
+        <v>-0.02045477997078363</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.01204346496634047</v>
+        <v>-0.0001794265869339149</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.08494839758213099</v>
+        <v>0.2087490889169464</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1296,19 +1296,19 @@
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.08019415767182966</v>
+        <v>-0.1200363463694608</v>
       </c>
       <c r="CW2" t="n">
         <v>-0</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.01449110875445229</v>
+        <v>0.1222014785353276</v>
       </c>
       <c r="CY2" t="n">
         <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.07185907948427746</v>
+        <v>-0.04091338776754098</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
@@ -1317,31 +1317,31 @@
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.0197792617355772</v>
+        <v>-0.06728186191024073</v>
       </c>
       <c r="DF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0.005441848683853862</v>
+        <v>0.03468946684040551</v>
       </c>
       <c r="DH2" t="n">
         <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.2155073792698327</v>
+        <v>-0.06666180313275381</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
@@ -1350,19 +1350,19 @@
         <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.001662442552179757</v>
+        <v>-0.05081962403062194</v>
       </c>
       <c r="DO2" t="n">
         <v>0</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0.06111066735414698</v>
+        <v>0.09312676206423191</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.04343742170409236</v>
+        <v>-0.1100972612658007</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
@@ -1374,22 +1374,22 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.00584555170886496</v>
+        <v>0.03601233385711521</v>
       </c>
       <c r="DX2" t="n">
         <v>-0</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.03939320441825435</v>
+        <v>0.1994648423370964</v>
       </c>
       <c r="DZ2" t="n">
         <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02010620157902848</v>
+        <v>0.08216605590952557</v>
       </c>
       <c r="EB2" t="n">
         <v>-0</v>
@@ -1398,55 +1398,55 @@
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.1086990077623373</v>
+        <v>-0.05807358886171687</v>
       </c>
       <c r="EG2" t="n">
         <v>-0</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.02987512601048106</v>
+        <v>0.05651728232020939</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.08053000172781083</v>
+        <v>0.08818484693769552</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.003925775806659581</v>
+        <v>-0.1200381275597719</v>
       </c>
       <c r="EP2" t="n">
         <v>0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0.04093221294384863</v>
+        <v>0.1080416882900602</v>
       </c>
       <c r="ER2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.09961256693128062</v>
+        <v>0.04547125099785961</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
@@ -1455,49 +1455,49 @@
         <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0.08607956601556029</v>
+        <v>-0.1095443321539509</v>
       </c>
       <c r="EY2" t="n">
         <v>0</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.006865342461180995</v>
+        <v>0.1004685572971014</v>
       </c>
       <c r="FA2" t="n">
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.09037236036276663</v>
+        <v>-0.04105324198199198</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0.1038846675298418</v>
+        <v>-0.08556450654293025</v>
       </c>
       <c r="FH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI2" t="n">
-        <v>-0.06909152253163407</v>
+        <v>0.0276771680789801</v>
       </c>
       <c r="FJ2" t="n">
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.1618662348347472</v>
+        <v>-0.02838787363983632</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
@@ -1509,25 +1509,25 @@
         <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0.0274584767942418</v>
+        <v>-0.03048752300200698</v>
       </c>
       <c r="FQ2" t="n">
         <v>-0</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0.03626007568056401</v>
+        <v>0.05968391960957806</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.1229326928428442</v>
+        <v>-0.2938828095530418</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
         <v>0</v>
@@ -1539,19 +1539,19 @@
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.06684391638481058</v>
+        <v>-0.1136632234559883</v>
       </c>
       <c r="FZ2" t="n">
         <v>0</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.07532372824077511</v>
+        <v>0.03999482140999734</v>
       </c>
       <c r="GB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
@@ -2140,154 +2140,154 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2197667908849288</v>
+        <v>0.5578233739821539</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06763846107580557</v>
+        <v>-0.002276327687486007</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04778675991960982</v>
+        <v>0.06526552827665759</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06871271768981697</v>
+        <v>-0.2160888884973607</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1277587378901571</v>
+        <v>0.4993542099199259</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05462433734185475</v>
+        <v>-0.1120233051405439</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02946027265860778</v>
+        <v>-0.04205129660193223</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.04317462987899704</v>
+        <v>-0.1126920379458048</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04937144377824131</v>
+        <v>0.1385991341198753</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.01514882904960532</v>
+        <v>-0.1466654076126097</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02754256094888084</v>
+        <v>-0.1434895456064261</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02309280354320864</v>
+        <v>0.006694252528539393</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01840914406672245</v>
+        <v>0.1465613418905699</v>
       </c>
       <c r="AD4" t="n">
         <v>-0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.04367134585154401</v>
+        <v>-0.3394198412530866</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.00125026988709313</v>
+        <v>-0.2172587604576743</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.0119005617031316</v>
+        <v>-0.1541780242071397</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001656097944060184</v>
+        <v>0.2670730249954267</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03113131002247291</v>
+        <v>-0.1450366566588353</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01359647667537389</v>
+        <v>0.1670010875248334</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.02883069633471027</v>
+        <v>-0.1910001426642614</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.3244104642102168</v>
+        <v>0.8155728531843117</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.009397941958847021</v>
+        <v>-0.004228945384757997</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.04677756664568994</v>
+        <v>-0.1414491872986918</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.04363053488610782</v>
+        <v>-0.1224664155625487</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,58 +2296,58 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02025646108011033</v>
+        <v>0.01816792888228675</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.04292178833260405</v>
+        <v>-0.0916837570388969</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.09432179855542493</v>
+        <v>-0.1375731519483069</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.1236468880906035</v>
+        <v>-0.2544931411963827</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.07009425816355222</v>
+        <v>0.03899142412124584</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.04521396862708939</v>
+        <v>-0.002509924346538094</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.06597463524192362</v>
+        <v>0.1470223782879805</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01369774018282329</v>
+        <v>0.009761877696496859</v>
       </c>
       <c r="BR4" t="n">
         <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2356,19 +2356,19 @@
         <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1198428804506877</v>
+        <v>0.3776346301940939</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.02495097964529424</v>
+        <v>-0.086450497649896</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01273602252141491</v>
+        <v>-0.009874549155010388</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.02348861010011724</v>
+        <v>-0.1655355969374503</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2377,28 +2377,28 @@
         <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.05866956524858317</v>
+        <v>-0.2702416595451853</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.006510601720493901</v>
+        <v>0.04023978871117893</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.001319947976155638</v>
+        <v>-0.06583626314199072</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.04405373934626156</v>
+        <v>0.1165501145961387</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -2407,301 +2407,301 @@
         <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.02195677800762075</v>
+        <v>-0.1933365221164951</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.03441075806007817</v>
+        <v>0.139470317511012</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.01931733497489368</v>
+        <v>0.01906795409302841</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.0164019664527915</v>
+        <v>0.08857434423209844</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.05104901735226843</v>
+        <v>-0.2450263319433091</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02359816977854992</v>
+        <v>0.04563486735221417</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.004730084119904106</v>
+        <v>-0.08257239161756685</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.05180191264958028</v>
+        <v>0.1122135875887873</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01321611014989833</v>
+        <v>-0.048787806640476</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.07826675187084432</v>
+        <v>-0.02973966325784675</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.01561664936553353</v>
+        <v>0.4731048605914669</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.003009584250383389</v>
+        <v>0.02178720578549196</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.03798320532819007</v>
+        <v>-0.09494536045495842</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.02724777894867367</v>
+        <v>0.06337540368320493</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0227020118237608</v>
+        <v>-0.09776319057018079</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.02653254520503731</v>
+        <v>0.1543843604885614</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.006054731141806383</v>
+        <v>0.1476123856479851</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.002795734057268609</v>
+        <v>0.07060383409165563</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.03584555947100912</v>
+        <v>0.01682263222457325</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.00258541826303072</v>
+        <v>-0.01521958738026408</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.08593620734471746</v>
+        <v>-0.114526649424992</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.03471547948101402</v>
+        <v>0.07162425893107426</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0367353333852423</v>
+        <v>-0.1009926891466333</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.008353643140979465</v>
+        <v>-0.02670890678746801</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.03584935300058535</v>
+        <v>-0.09565654023149291</v>
       </c>
       <c r="EQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0003255704418690113</v>
+        <v>-0.08395119485912086</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.004785980301531378</v>
+        <v>-0.07426719753134392</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.06831097152479307</v>
+        <v>0.2493991858716779</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.04709916610512214</v>
+        <v>-0.2822239029585729</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.00705408079461627</v>
+        <v>0.0427143634043378</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.01414332293081877</v>
+        <v>-0.1164456146798406</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.04210197371695123</v>
+        <v>0.08940379044054639</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.03531574651317242</v>
+        <v>-0.2221661969964162</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.03391435740103591</v>
+        <v>0.1418176003039721</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.003532563844474296</v>
+        <v>-0.03954314121581561</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.00800320829410152</v>
+        <v>0.3488679216806419</v>
       </c>
       <c r="FM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.006610866519397472</v>
+        <v>-0.1847785072457316</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.01631024947911528</v>
+        <v>0.2851599745447508</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.006098666960557544</v>
+        <v>0.006130310389735823</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0003246674849548178</v>
+        <v>0.08912753497891127</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.03548492396418154</v>
+        <v>-0.09927253597834998</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02308780334112119</v>
+        <v>-0.194549181245576</v>
       </c>
       <c r="GC4" t="n">
         <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.001559574311184672</v>
+        <v>-0.08116691836157176</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3275,10 +3275,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.6333321328806398</v>
+        <v>-0.2084792159555122</v>
       </c>
       <c r="C6" t="n">
         <v>-0</v>
@@ -3287,13 +3287,13 @@
         <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1440645318562985</v>
+        <v>-0.006384425030151558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9478170162920985</v>
+        <v>0.189834941200862</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3302,10 +3302,10 @@
         <v>-0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2768047235892421</v>
+        <v>-0.1096166751430972</v>
       </c>
       <c r="L6" t="n">
         <v>-0</v>
@@ -3314,10 +3314,10 @@
         <v>-0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04714759552105241</v>
+        <v>0.04994366285250167</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6130080528745286</v>
+        <v>0.1275513823510485</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
@@ -3332,22 +3332,22 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.08987364958049784</v>
+        <v>-0.07447894772877092</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
         <v>-0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.09929075318987055</v>
+        <v>-0.01028612858590421</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01322540642381054</v>
+        <v>-0.03034365880860297</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -3356,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.2292662844646398</v>
+        <v>0.04934224178435086</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
@@ -3368,10 +3368,10 @@
         <v>-0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.009041921356546138</v>
+        <v>0.1325664531607018</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1794684588853131</v>
+        <v>0.02895627485620352</v>
       </c>
       <c r="AH6" t="n">
         <v>-0</v>
@@ -3386,22 +3386,22 @@
         <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.1023697505229313</v>
+        <v>-0.1064408785403294</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.133995609998641</v>
+        <v>-0.06988470441452106</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.2848560101649846</v>
+        <v>0.1473352732760574</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.3965576578619361</v>
+        <v>-0.2712167576070214</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,25 +3422,25 @@
         <v>-0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.3715169595648701</v>
+        <v>0.08545254241921577</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.898446928044848</v>
+        <v>0.1229258411756775</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.407520166372013</v>
+        <v>0.08502860584449448</v>
       </c>
       <c r="BE6" t="n">
         <v>-0</v>
@@ -3449,25 +3449,25 @@
         <v>-0</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.1853226290135963</v>
+        <v>0.1992327461192683</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.1937053163495445</v>
+        <v>0.1106634423137898</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1100656542514048</v>
+        <v>0.01639344190314307</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.1007975938249138</v>
+        <v>-0.05520747974159876</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.003827582056926658</v>
+        <v>-0.04510861521099055</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
@@ -3494,25 +3494,25 @@
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.2135037216207077</v>
+        <v>-0.2043496119656293</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
         <v>-0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1011905607977777</v>
+        <v>0.004108661655667133</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.3343115544923815</v>
+        <v>0.08431087855857648</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC6" t="n">
         <v>-0</v>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.1917405269793536</v>
+        <v>0.1225254342914704</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
@@ -3530,10 +3530,10 @@
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.01392885338782887</v>
+        <v>-0.01319583423710121</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.1923463616915325</v>
+        <v>-0.07743273012909681</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
@@ -3542,28 +3542,28 @@
         <v>-0</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM6" t="n">
         <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01870983651228235</v>
+        <v>0.0735202445044103</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP6" t="n">
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.2128664555115923</v>
+        <v>-0.1443724349365737</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1178104982967436</v>
+        <v>-0.04107696025664406</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
@@ -3572,10 +3572,10 @@
         <v>0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.1588111466996637</v>
+        <v>0.1107408049406598</v>
       </c>
       <c r="CX6" t="n">
         <v>-0</v>
@@ -3584,10 +3584,10 @@
         <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.06267377383661794</v>
+        <v>-0.01041636696222213</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0.2316167622665714</v>
+        <v>-0.06522510937247344</v>
       </c>
       <c r="DB6" t="n">
         <v>-0</v>
@@ -3602,52 +3602,52 @@
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01400185717823196</v>
+        <v>-0.003995657365040254</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.2584495789923995</v>
+        <v>0.0498187860226145</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.03326402031973864</v>
+        <v>-0.01065246494434375</v>
       </c>
       <c r="DK6" t="n">
         <v>-0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.1236803356152932</v>
+        <v>0.02124188153493036</v>
       </c>
       <c r="DP6" t="n">
         <v>0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.1041139570545863</v>
+        <v>0.007669797168659903</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.06952409350688951</v>
+        <v>-0.02506587373349488</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.1309708494361494</v>
+        <v>-0.03391614190114071</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,10 +3665,10 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.2929865533099328</v>
+        <v>0.0497579787310474</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.1000511045917228</v>
+        <v>0.02212487484629061</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
@@ -3677,25 +3677,25 @@
         <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0793975541923761</v>
+        <v>0.05819865071308115</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.1459935794740662</v>
+        <v>0.01846939864496878</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.1644080759119566</v>
+        <v>-0.01011193822996479</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
@@ -3704,13 +3704,13 @@
         <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.1711079067931622</v>
+        <v>0.09367782183312537</v>
       </c>
       <c r="EQ6" t="n">
         <v>0</v>
@@ -3719,25 +3719,25 @@
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.08809072694169402</v>
+        <v>0.07162776965567434</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.006277793455702759</v>
+        <v>0.09626699634157608</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.178110070323006</v>
+        <v>0.1272744353608633</v>
       </c>
       <c r="EZ6" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.05886863043145255</v>
+        <v>-0.003162623344727291</v>
       </c>
       <c r="FC6" t="n">
-        <v>-0.2320116557213362</v>
+        <v>-0.06032154245826478</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.01800079849460328</v>
+        <v>0.1259115030178628</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,37 +3773,37 @@
         <v>0</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.01501975987369351</v>
+        <v>-0.04267275441389723</v>
       </c>
       <c r="FL6" t="n">
-        <v>-0.2392463723158225</v>
+        <v>-0.0993115145385092</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.008423739451268418</v>
+        <v>0.1100794135240663</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.1484080108072988</v>
+        <v>-0.01005489410683047</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0.3303382599966145</v>
+        <v>-0.07058023032862215</v>
       </c>
       <c r="FV6" t="n">
         <v>0</v>
@@ -3818,10 +3818,10 @@
         <v>-0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.1283005601406513</v>
+        <v>0.113629337868941</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0872130603933849</v>
+        <v>0.03830205089082456</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3844,22 +3844,22 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1333747704097537</v>
+        <v>0.5148325973131788</v>
       </c>
       <c r="C7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.006346353310403234</v>
+        <v>0.0002700440850149603</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.09238705329937291</v>
+        <v>-0.280564342159551</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3871,10 +3871,10 @@
         <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1074339899046069</v>
+        <v>0.6075606347199339</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,16 +3883,16 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.004922750975620268</v>
+        <v>-0.1269468041886106</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.06333348995726427</v>
+        <v>-0.1982353532227623</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>-0</v>
@@ -3901,7 +3901,7 @@
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007850565653307266</v>
+        <v>0.1139995950450614</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,16 +3910,16 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01521090670274852</v>
+        <v>-0.004443227824983744</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.01571716032506547</v>
+        <v>-0.1177768790472474</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -3928,19 +3928,19 @@
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.008316099349665495</v>
+        <v>0.03215875159809943</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01235721675422421</v>
+        <v>-0.06130712917934466</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01731685655992342</v>
+        <v>0.07795744972795222</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.006742006836319209</v>
+        <v>0.1657124953135528</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.008719181063579343</v>
+        <v>0.06451357517745945</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.04350250535089837</v>
+        <v>-0.09482639186049169</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,37 +3979,37 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1091571088354197</v>
+        <v>0.7338388647635505</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.00885172471062848</v>
+        <v>-0.2759153201846885</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.06423155134413359</v>
+        <v>-0.3212020212138874</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
         <v>-0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05188276019307981</v>
+        <v>-0.1839698045602423</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,10 +4018,10 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.02485971350127424</v>
+        <v>0.01335580953829206</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.05555194651347658</v>
+        <v>-0.0419011910793562</v>
       </c>
       <c r="BI7" t="n">
         <v>-0</v>
@@ -4030,52 +4030,52 @@
         <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03996804065148661</v>
+        <v>0.009174731277238977</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01419698175298306</v>
+        <v>0.089843474575002</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01794783304865634</v>
+        <v>0.04391066948069087</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05605944782850338</v>
+        <v>0.4384048668309342</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.002626131867736737</v>
+        <v>-0.03677873754959628</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.02406693501916508</v>
+        <v>-0.1703999915772176</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4090,25 +4090,25 @@
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02983591228312463</v>
+        <v>-0.2394700460300695</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.00271046045514352</v>
+        <v>0.017515858575498</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.02423289219041722</v>
+        <v>0.1075699391986752</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL7" t="n">
         <v>0</v>
@@ -4117,61 +4117,61 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.008574699962323611</v>
+        <v>-0.09829052415643967</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.00351575685253533</v>
+        <v>0.07772980135248647</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.008853434160957165</v>
+        <v>0.04492254828031166</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.0223002523975217</v>
+        <v>-0.2237061299253223</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.0022845470218262</v>
+        <v>0.01441453771117305</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.02978972586931386</v>
+        <v>0.1233328294515248</v>
       </c>
       <c r="DB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.004042153493190569</v>
+        <v>0.01108555135666103</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
@@ -4180,10 +4180,10 @@
         <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.008102356115746018</v>
+        <v>0.02229123519137749</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0126818434258586</v>
+        <v>0.09452965097261611</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4195,28 +4195,28 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.0117108452349807</v>
+        <v>-0.08465824679981289</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.007697112199631012</v>
+        <v>-0.0183323931389147</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.004775339957483572</v>
+        <v>0.08594244480854549</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,46 +4225,46 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.03625581567067365</v>
+        <v>-0.1572603468630954</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.009218750434680942</v>
+        <v>0.06259317427101001</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.01784494534518465</v>
+        <v>-0.1024368562931136</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02071768898491964</v>
+        <v>-0.1283539480535044</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.003104876901817064</v>
+        <v>-0.05031721999726278</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0156409895730309</v>
+        <v>0.0412747467355729</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
@@ -4279,19 +4279,19 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.007571463270012959</v>
+        <v>0.0938704795640192</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.003932367996226053</v>
+        <v>0.0142643575323563</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.001880821807891714</v>
+        <v>-0.04128950148844369</v>
       </c>
       <c r="EU7" t="n">
         <v>0</v>
@@ -4300,52 +4300,52 @@
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX7" t="n">
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02198731072545749</v>
+        <v>-0.2578804784633106</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.001206428374172076</v>
+        <v>-0.007625591026963668</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.03021805443850384</v>
+        <v>0.1250087453308819</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.003380217103684103</v>
+        <v>-0.1260089855804763</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01607362177234817</v>
+        <v>-0.01451814246354441</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.02992896954521935</v>
+        <v>0.1362518640586858</v>
       </c>
       <c r="FM7" t="n">
         <v>-0</v>
@@ -4360,7 +4360,7 @@
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.0196555951489811</v>
+        <v>-0.2368096317537156</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,37 +4369,37 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.02443977178562185</v>
+        <v>-0.06122378289717301</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0.0008763209283351258</v>
+        <v>-0.0101744704646738</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.01311891922634132</v>
+        <v>-0.1134967812113027</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.02613882249697758</v>
+        <v>0.07198302679113594</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
@@ -4408,7 +4408,7 @@
         <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,16 +4416,16 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.3595239659945326</v>
+        <v>-0.3737637328004914</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1918948061953517</v>
+        <v>0.1326478602353585</v>
       </c>
       <c r="E8" t="n">
-        <v>0.217961686878524</v>
+        <v>0.07984689236739811</v>
       </c>
       <c r="F8" t="n">
         <v>-0</v>
@@ -4437,25 +4437,25 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.290603672443886</v>
+        <v>-0.4559974253514154</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2105292914795927</v>
+        <v>0.223032096262105</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2389788726610567</v>
+        <v>0.1539367503506809</v>
       </c>
       <c r="O8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -4470,25 +4470,25 @@
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1015994294792082</v>
+        <v>-0.0402388324492669</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01694052201451101</v>
+        <v>0.01267256161566748</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.04183647001244236</v>
+        <v>-0.005544661424828436</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>-0</v>
@@ -4497,22 +4497,22 @@
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1524543817303817</v>
+        <v>-0.01986218768638529</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.05730643156480612</v>
+        <v>0.1338706937573633</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.03112473842292171</v>
+        <v>-0.2222037577602377</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -4521,76 +4521,76 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.03530618224662264</v>
+        <v>-0.1467362683141169</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.04496369266459647</v>
+        <v>0.03771858075953894</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.07773047799036843</v>
+        <v>-0.2313778420852493</v>
       </c>
       <c r="AP8" t="n">
         <v>-0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.2823760744888923</v>
+        <v>-0.2428530737293749</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.009386233642463646</v>
+        <v>0.140834232216819</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.01912585227520819</v>
+        <v>0.02256290232743481</v>
       </c>
       <c r="AY8" t="n">
         <v>-0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01270378074326078</v>
+        <v>0.05066757266978159</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.1947370835745189</v>
+        <v>0.01267303549555298</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.2801864307627785</v>
+        <v>0.131204742198662</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
@@ -4605,16 +4605,16 @@
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0.09746939744970234</v>
+        <v>0.1121550478169164</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>-0.03966367599017617</v>
+        <v>0.08290456634644046</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.1006469971429728</v>
+        <v>0.001854649371135884</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
@@ -4632,25 +4632,25 @@
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>-0.2214552231237848</v>
+        <v>-0.1967383025962886</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001954980983664282</v>
+        <v>0.06910249671461589</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.04295490695730891</v>
+        <v>-0.0085159241749709</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC8" t="n">
         <v>-0</v>
@@ -4659,25 +4659,25 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.09111559250187642</v>
+        <v>0.1941410410625169</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>-0.04630099311145542</v>
+        <v>-0.05770707510185234</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002501104486842532</v>
+        <v>-0.004755495526076575</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL8" t="n">
         <v>0</v>
@@ -4686,19 +4686,19 @@
         <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.03036194770759994</v>
+        <v>0.089814116304601</v>
       </c>
       <c r="CO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.06177633397348618</v>
+        <v>-0.08566313376769037</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.08264093758651204</v>
+        <v>-0.03688885645439984</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.08768772856841285</v>
+        <v>0.203680935099142</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0.06427216599515229</v>
+        <v>-0.05883352196937213</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.003251567564702623</v>
+        <v>-0.03258943965871855</v>
       </c>
       <c r="DA8" t="n">
         <v>-0</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,52 +4740,52 @@
         <v>-0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.1674791704590838</v>
+        <v>0.1516227042501961</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0.05120534549396998</v>
+        <v>-0.02342471104732869</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.008569236863323306</v>
+        <v>-0.000970404644517681</v>
       </c>
       <c r="DJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL8" t="n">
         <v>-0</v>
       </c>
       <c r="DM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0444027720261606</v>
+        <v>0.09032915425264003</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.03951346969164644</v>
+        <v>-0.04203099856430466</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.06924336164510286</v>
+        <v>0.02707078849941816</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV8" t="n">
         <v>-0</v>
@@ -4794,22 +4794,22 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.1020258637098203</v>
+        <v>0.04218837314236253</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.09150862549650279</v>
+        <v>0.04949671606083903</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.05065278254419057</v>
+        <v>0.006867971764129158</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
         <v>-0</v>
@@ -4821,22 +4821,22 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.05382829121024003</v>
+        <v>0.2267285513372236</v>
       </c>
       <c r="EH8" t="n">
         <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.04169300521635982</v>
+        <v>-0.0568662035802833</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.1036737619249987</v>
+        <v>-0.03789969876844101</v>
       </c>
       <c r="EK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM8" t="n">
         <v>0</v>
@@ -4845,28 +4845,28 @@
         <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0004639062558998706</v>
+        <v>-0.1168263580159574</v>
       </c>
       <c r="EQ8" t="n">
         <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.03281302057021471</v>
+        <v>-0.01012929929656321</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.02831961310528018</v>
+        <v>0.004782772460820705</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
@@ -4875,16 +4875,16 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.09068410370469708</v>
+        <v>0.2302553806432373</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>-0.05954802278726774</v>
+        <v>-0.0707934113191805</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.005773934316406578</v>
+        <v>-0.0006280483128592738</v>
       </c>
       <c r="FC8" t="n">
         <v>0</v>
@@ -4893,52 +4893,52 @@
         <v>-0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG8" t="n">
         <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.05169731641457217</v>
+        <v>0.08428186888562736</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.08810583646586569</v>
+        <v>0.1085450814762721</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.04179208425015184</v>
+        <v>0.03676015370198812</v>
       </c>
       <c r="FL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.02522769737549652</v>
+        <v>0.1785516605937419</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.03322027598198776</v>
+        <v>0.01260390136827294</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.009205554983633504</v>
+        <v>-0.05637390529607172</v>
       </c>
       <c r="FU8" t="n">
         <v>0</v>
@@ -4947,37 +4947,37 @@
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
         <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.05225639164725931</v>
+        <v>0.2022148667834</v>
       </c>
       <c r="GA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.06616922842704878</v>
+        <v>-0.001531745628289719</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE8" t="n">
         <v>0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,16 +4994,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,16 +5048,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,19 +5066,19 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH9" t="n">
         <v>-0</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
@@ -5117,10 +5117,10 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
@@ -5129,16 +5129,16 @@
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,100 +5255,100 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM9" t="n">
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5357,13 +5357,13 @@
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,106 +5372,106 @@
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
@@ -5480,16 +5480,16 @@
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
@@ -5498,46 +5498,46 @@
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
@@ -5546,7 +5546,7 @@
         <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,25 +6701,25 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -6755,40 +6755,40 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X12" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD12" t="n">
         <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6800,22 +6800,22 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,28 +6824,28 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,52 +6863,52 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6929,31 +6929,31 @@
         <v>-0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL12" t="n">
         <v>0</v>
@@ -6962,52 +6962,52 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,22 +7016,22 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
         <v>-0</v>
@@ -7040,28 +7040,28 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>-0</v>
@@ -7070,49 +7070,49 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,82 +7121,82 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
@@ -7205,63 +7205,63 @@
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7282,10 +7282,10 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K13" t="n">
         <v>-0</v>
@@ -7294,43 +7294,43 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -7348,43 +7348,43 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7393,25 +7393,25 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
@@ -7420,22 +7420,22 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
@@ -7447,10 +7447,10 @@
         <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,37 +7459,37 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,10 +7498,10 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE13" t="n">
         <v>0</v>
@@ -7513,13 +7513,13 @@
         <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7528,25 +7528,25 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
@@ -7555,7 +7555,7 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW13" t="n">
         <v>-0</v>
@@ -7567,40 +7567,40 @@
         <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7609,7 +7609,7 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO13" t="n">
         <v>0</v>
@@ -7618,13 +7618,13 @@
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7633,37 +7633,37 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY13" t="n">
         <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE13" t="n">
         <v>0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG13" t="n">
         <v>0</v>
@@ -7675,22 +7675,22 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP13" t="n">
         <v>0</v>
@@ -7699,13 +7699,13 @@
         <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7717,7 +7717,7 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY13" t="n">
         <v>0</v>
@@ -7729,22 +7729,22 @@
         <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH13" t="n">
         <v>-0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
@@ -7771,10 +7771,10 @@
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,13 +7783,13 @@
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
         <v>-0</v>
@@ -7798,28 +7798,28 @@
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
